--- a/templates/teste-pratico-motoristas.xlsx
+++ b/templates/teste-pratico-motoristas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lemartransportes-my.sharepoint.com/personal/mario_viana_lemartransportes_com_br/Documents/DOWNLOADS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mario.viana\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{911F8901-067A-4866-8937-EF17FFE615A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9DB1D98-94E5-4D80-ABBA-75FF78267F0E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22189E2-0EA0-43C9-949B-C749142D4C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{94554CD0-EDC9-48DF-9D0D-9C8EE242D8BD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94554CD0-EDC9-48DF-9D0D-9C8EE242D8BD}"/>
   </bookViews>
   <sheets>
     <sheet name="ATUALIZADO MARÇO-2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Nome Candidato:</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>NÃO(   )</t>
+  </si>
+  <si>
+    <t>Obs:</t>
   </si>
 </sst>
 </file>
@@ -1311,6 +1314,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1397,81 +1475,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1818,82 +1821,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="61"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="86"/>
     </row>
     <row r="2" spans="1:8" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="64"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="89"/>
     </row>
     <row r="3" spans="1:8" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="64"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="89"/>
     </row>
     <row r="4" spans="1:8" ht="23.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="67"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="92"/>
     </row>
     <row r="5" spans="1:8" ht="23.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="70"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="95"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="73"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="98"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="75"/>
+      <c r="B7" s="100"/>
       <c r="C7" s="5">
         <v>1</v>
       </c>
@@ -1914,7 +1917,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="101" t="s">
         <v>31</v>
       </c>
       <c r="B8" s="47" t="s">
@@ -1928,7 +1931,7 @@
       <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="77"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="48" t="s">
         <v>33</v>
       </c>
@@ -1940,7 +1943,7 @@
       <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="77"/>
+      <c r="A10" s="102"/>
       <c r="B10" s="48" t="s">
         <v>34</v>
       </c>
@@ -1952,7 +1955,7 @@
       <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="77"/>
+      <c r="A11" s="102"/>
       <c r="B11" s="48" t="s">
         <v>35</v>
       </c>
@@ -1964,7 +1967,7 @@
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="77"/>
+      <c r="A12" s="102"/>
       <c r="B12" s="48" t="s">
         <v>36</v>
       </c>
@@ -1976,7 +1979,7 @@
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="78"/>
+      <c r="A13" s="103"/>
       <c r="B13" s="49" t="s">
         <v>37</v>
       </c>
@@ -1988,7 +1991,7 @@
       <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="101" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="47" t="s">
@@ -2002,7 +2005,7 @@
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="77"/>
+      <c r="A15" s="102"/>
       <c r="B15" s="48" t="s">
         <v>40</v>
       </c>
@@ -2014,7 +2017,7 @@
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="77"/>
+      <c r="A16" s="102"/>
       <c r="B16" s="48" t="s">
         <v>6</v>
       </c>
@@ -2026,7 +2029,7 @@
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="77"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="48" t="s">
         <v>41</v>
       </c>
@@ -2038,7 +2041,7 @@
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="77"/>
+      <c r="A18" s="102"/>
       <c r="B18" s="48" t="s">
         <v>42</v>
       </c>
@@ -2050,7 +2053,7 @@
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="77"/>
+      <c r="A19" s="102"/>
       <c r="B19" s="48" t="s">
         <v>7</v>
       </c>
@@ -2062,7 +2065,7 @@
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="77"/>
+      <c r="A20" s="102"/>
       <c r="B20" s="48" t="s">
         <v>43</v>
       </c>
@@ -2074,7 +2077,7 @@
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="78"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="49" t="s">
         <v>44</v>
       </c>
@@ -2086,7 +2089,7 @@
       <c r="H21" s="12"/>
     </row>
     <row r="22" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="101" t="s">
         <v>45</v>
       </c>
       <c r="B22" s="47" t="s">
@@ -2100,7 +2103,7 @@
       <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="77"/>
+      <c r="A23" s="102"/>
       <c r="B23" s="48" t="s">
         <v>9</v>
       </c>
@@ -2112,7 +2115,7 @@
       <c r="H23" s="20"/>
     </row>
     <row r="24" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="77"/>
+      <c r="A24" s="102"/>
       <c r="B24" s="48" t="s">
         <v>10</v>
       </c>
@@ -2124,7 +2127,7 @@
       <c r="H24" s="20"/>
     </row>
     <row r="25" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="77"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="48" t="s">
         <v>11</v>
       </c>
@@ -2136,7 +2139,7 @@
       <c r="H25" s="20"/>
     </row>
     <row r="26" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="77"/>
+      <c r="A26" s="102"/>
       <c r="B26" s="48" t="s">
         <v>12</v>
       </c>
@@ -2148,7 +2151,7 @@
       <c r="H26" s="20"/>
     </row>
     <row r="27" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="77"/>
+      <c r="A27" s="102"/>
       <c r="B27" s="48" t="s">
         <v>13</v>
       </c>
@@ -2160,7 +2163,7 @@
       <c r="H27" s="20"/>
     </row>
     <row r="28" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="77"/>
+      <c r="A28" s="102"/>
       <c r="B28" s="48" t="s">
         <v>14</v>
       </c>
@@ -2172,7 +2175,7 @@
       <c r="H28" s="20"/>
     </row>
     <row r="29" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="77"/>
+      <c r="A29" s="102"/>
       <c r="B29" s="48" t="s">
         <v>15</v>
       </c>
@@ -2184,7 +2187,7 @@
       <c r="H29" s="20"/>
     </row>
     <row r="30" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="77"/>
+      <c r="A30" s="102"/>
       <c r="B30" s="50" t="s">
         <v>16</v>
       </c>
@@ -2196,7 +2199,7 @@
       <c r="H30" s="23"/>
     </row>
     <row r="31" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="77"/>
+      <c r="A31" s="102"/>
       <c r="B31" s="50" t="s">
         <v>17</v>
       </c>
@@ -2208,7 +2211,7 @@
       <c r="H31" s="23"/>
     </row>
     <row r="32" spans="1:8" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="78"/>
+      <c r="A32" s="103"/>
       <c r="B32" s="49" t="s">
         <v>18</v>
       </c>
@@ -2220,97 +2223,99 @@
       <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="79" t="s">
+      <c r="A33" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="81"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="105"/>
+      <c r="H33" s="106"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="54"/>
+      <c r="B34" s="79"/>
       <c r="C34" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="55" t="s">
+      <c r="D34" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="56"/>
-      <c r="F34" s="55" t="s">
+      <c r="E34" s="81"/>
+      <c r="F34" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="G34" s="57"/>
-      <c r="H34" s="58"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="83"/>
     </row>
     <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="82" t="s">
+      <c r="A35" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="83"/>
+      <c r="B35" s="77"/>
       <c r="C35" s="28"/>
-      <c r="D35" s="84" t="s">
+      <c r="D35" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="E35" s="85"/>
-      <c r="F35" s="84" t="s">
+      <c r="E35" s="62"/>
+      <c r="F35" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="G35" s="86"/>
-      <c r="H35" s="85"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="62"/>
     </row>
     <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="87" t="s">
+      <c r="A36" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="88"/>
+      <c r="B36" s="60"/>
       <c r="C36" s="28"/>
-      <c r="D36" s="84" t="s">
+      <c r="D36" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="85"/>
-      <c r="F36" s="84" t="s">
+      <c r="E36" s="62"/>
+      <c r="F36" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="86"/>
-      <c r="H36" s="85"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="62"/>
     </row>
     <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="87" t="s">
+      <c r="A37" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="88"/>
+      <c r="B37" s="60"/>
       <c r="C37" s="28"/>
-      <c r="D37" s="84" t="s">
+      <c r="D37" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="85"/>
-      <c r="F37" s="84" t="s">
+      <c r="E37" s="62"/>
+      <c r="F37" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="G37" s="86"/>
-      <c r="H37" s="85"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="62"/>
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="87" t="s">
+      <c r="A38" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="B38" s="88"/>
-      <c r="C38" s="95"/>
-      <c r="D38" s="96"/>
-      <c r="E38" s="96"/>
-      <c r="F38" s="96"/>
-      <c r="G38" s="96"/>
-      <c r="H38" s="97"/>
+      <c r="B38" s="60"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="66"/>
     </row>
     <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="29"/>
+      <c r="A39" s="29" t="s">
+        <v>57</v>
+      </c>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
       <c r="D39" s="30"/>
@@ -2345,12 +2350,12 @@
     </row>
     <row r="43" spans="1:8" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="34"/>
-      <c r="B43" s="89" t="s">
+      <c r="B43" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C43" s="90"/>
-      <c r="D43" s="90"/>
-      <c r="E43" s="91"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="55"/>
       <c r="F43" s="41" t="s">
         <v>55</v>
       </c>
@@ -2361,12 +2366,12 @@
     </row>
     <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="40"/>
-      <c r="B44" s="89" t="s">
+      <c r="B44" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="90"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="55"/>
       <c r="F44" s="41" t="s">
         <v>55</v>
       </c>
@@ -2407,24 +2412,24 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="32"/>
-      <c r="B48" s="98" t="s">
+      <c r="B48" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="99"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="100"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="68"/>
+      <c r="G48" s="69"/>
       <c r="H48" s="33"/>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="32"/>
-      <c r="B49" s="101"/>
-      <c r="C49" s="102"/>
-      <c r="D49" s="102"/>
-      <c r="E49" s="102"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="103"/>
+      <c r="B49" s="70"/>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="72"/>
       <c r="H49" s="33"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
@@ -2438,26 +2443,26 @@
       <c r="H50" s="33"/>
     </row>
     <row r="51" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="104" t="s">
+      <c r="A51" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="105"/>
-      <c r="C51" s="105"/>
-      <c r="D51" s="105"/>
-      <c r="E51" s="105"/>
-      <c r="F51" s="105"/>
-      <c r="G51" s="105"/>
-      <c r="H51" s="106"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="74"/>
+      <c r="H51" s="75"/>
     </row>
     <row r="52" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="92"/>
-      <c r="B52" s="93"/>
-      <c r="C52" s="93"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="93"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="93"/>
-      <c r="H52" s="94"/>
+      <c r="A52" s="56"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="58"/>
     </row>
     <row r="53" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="29"/>
@@ -2741,22 +2746,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="B48:G49"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="F34:H34"/>
@@ -2771,6 +2760,22 @@
     <mergeCell ref="A14:A21"/>
     <mergeCell ref="A22:A32"/>
     <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="B48:G49"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="B43:E43"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/templates/teste-pratico-motoristas.xlsx
+++ b/templates/teste-pratico-motoristas.xlsx
@@ -15,6 +15,9 @@
   <sheets>
     <sheet name="ATUALIZADO MARÇO-2025" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ATUALIZADO MARÇO-2025'!$A$1:$H$77</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1156,7 +1159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1475,6 +1478,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1810,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93870B26-7C85-41EC-983A-E51F9F679233}">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="1" customWidth="1"/>
@@ -2390,362 +2402,324 @@
       <c r="G45" s="43"/>
       <c r="H45" s="43"/>
     </row>
-    <row r="46" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="43"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
-    </row>
-    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="36"/>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="38"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="32"/>
-      <c r="B48" s="67" t="s">
-        <v>54</v>
-      </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="33"/>
-    </row>
-    <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="32"/>
-      <c r="B49" s="70"/>
-      <c r="C49" s="71"/>
-      <c r="D49" s="71"/>
-      <c r="E49" s="71"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="72"/>
-      <c r="H49" s="33"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="32"/>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="33"/>
-    </row>
-    <row r="51" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="73" t="s">
+    <row r="46" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="74"/>
-      <c r="C51" s="74"/>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="74"/>
-      <c r="H51" s="75"/>
-    </row>
-    <row r="52" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="56"/>
-      <c r="B52" s="57"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="58"/>
-    </row>
-    <row r="53" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="29"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="31"/>
-    </row>
-    <row r="54" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="29"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="31"/>
-    </row>
-    <row r="55" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="29"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="31"/>
-    </row>
-    <row r="56" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="29"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
-      <c r="H56" s="31"/>
-    </row>
-    <row r="57" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="4"/>
-    </row>
-    <row r="58" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="4"/>
-    </row>
-    <row r="59" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="4"/>
-    </row>
-    <row r="60" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="4"/>
-    </row>
-    <row r="61" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="4"/>
-    </row>
-    <row r="62" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="2"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="4"/>
-    </row>
-    <row r="63" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="4"/>
-    </row>
-    <row r="64" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="4"/>
-    </row>
-    <row r="65" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="2"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="4"/>
-    </row>
-    <row r="66" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="4"/>
-    </row>
-    <row r="67" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="4"/>
-    </row>
-    <row r="68" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="2"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="4"/>
-    </row>
-    <row r="69" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="4"/>
-    </row>
-    <row r="70" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="2"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="4"/>
-    </row>
-    <row r="72" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="2"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="4"/>
-    </row>
-    <row r="73" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="2"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="4"/>
-    </row>
-    <row r="74" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="2"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="4"/>
-    </row>
-    <row r="75" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="2"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="4"/>
-    </row>
-    <row r="76" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="2"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="4"/>
-    </row>
-    <row r="77" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="2"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="4"/>
-    </row>
-    <row r="78" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="2"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="4"/>
-    </row>
-    <row r="79" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="4"/>
-    </row>
-    <row r="80" spans="1:8" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="44"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="45"/>
-      <c r="D80" s="45"/>
-      <c r="E80" s="45"/>
-      <c r="F80" s="45"/>
-      <c r="G80" s="45"/>
-      <c r="H80" s="46"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="75"/>
+    </row>
+    <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARECER</t>
+        </is>
+      </c>
+      <c r="B47" s="107"/>
+      <c r="C47" s="107"/>
+      <c r="D47" s="107"/>
+      <c r="E47" s="107"/>
+      <c r="F47" s="107"/>
+      <c r="G47" s="107"/>
+      <c r="H47" s="107"/>
+    </row>
+    <row r="48" spans="1:8" ht="10" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nome:</t>
+        </is>
+      </c>
+      <c r="B49" s="108"/>
+      <c r="C49" s="109"/>
+      <c r="D49" s="109"/>
+      <c r="E49" s="109"/>
+      <c r="F49" s="109"/>
+      <c r="G49" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data:</t>
+        </is>
+      </c>
+      <c r="H49" s="109"/>
+    </row>
+    <row r="50" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="109"/>
+      <c r="B51" s="109"/>
+      <c r="C51" s="109"/>
+      <c r="D51" s="109"/>
+      <c r="E51" s="109"/>
+      <c r="F51" s="109"/>
+      <c r="G51" s="109"/>
+      <c r="H51" s="109"/>
+    </row>
+    <row r="52" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="109"/>
+      <c r="B52" s="109"/>
+      <c r="C52" s="109"/>
+      <c r="D52" s="109"/>
+      <c r="E52" s="109"/>
+      <c r="F52" s="109"/>
+      <c r="G52" s="109"/>
+      <c r="H52" s="109"/>
+    </row>
+    <row r="53" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="109"/>
+      <c r="B53" s="109"/>
+      <c r="C53" s="109"/>
+      <c r="D53" s="109"/>
+      <c r="E53" s="109"/>
+      <c r="F53" s="109"/>
+      <c r="G53" s="109"/>
+      <c r="H53" s="109"/>
+    </row>
+    <row r="54" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="109"/>
+      <c r="B54" s="109"/>
+      <c r="C54" s="109"/>
+      <c r="D54" s="109"/>
+      <c r="E54" s="109"/>
+      <c r="F54" s="109"/>
+      <c r="G54" s="109"/>
+      <c r="H54" s="109"/>
+    </row>
+    <row r="55" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="109"/>
+      <c r="B55" s="109"/>
+      <c r="C55" s="109"/>
+      <c r="D55" s="109"/>
+      <c r="E55" s="109"/>
+      <c r="F55" s="109"/>
+      <c r="G55" s="109"/>
+      <c r="H55" s="109"/>
+    </row>
+    <row r="56" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="109"/>
+      <c r="B56" s="109"/>
+      <c r="C56" s="109"/>
+      <c r="D56" s="109"/>
+      <c r="E56" s="109"/>
+      <c r="F56" s="109"/>
+      <c r="G56" s="109"/>
+      <c r="H56" s="109"/>
+    </row>
+    <row r="57" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="109"/>
+      <c r="B57" s="109"/>
+      <c r="C57" s="109"/>
+      <c r="D57" s="109"/>
+      <c r="E57" s="109"/>
+      <c r="F57" s="109"/>
+      <c r="G57" s="109"/>
+      <c r="H57" s="109"/>
+    </row>
+    <row r="58" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="109"/>
+      <c r="B58" s="109"/>
+      <c r="C58" s="109"/>
+      <c r="D58" s="109"/>
+      <c r="E58" s="109"/>
+      <c r="F58" s="109"/>
+      <c r="G58" s="109"/>
+      <c r="H58" s="109"/>
+    </row>
+    <row r="59" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="109"/>
+      <c r="B59" s="109"/>
+      <c r="C59" s="109"/>
+      <c r="D59" s="109"/>
+      <c r="E59" s="109"/>
+      <c r="F59" s="109"/>
+      <c r="G59" s="109"/>
+      <c r="H59" s="109"/>
+    </row>
+    <row r="60" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="109"/>
+      <c r="B60" s="109"/>
+      <c r="C60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+    </row>
+    <row r="61" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="109"/>
+      <c r="B61" s="109"/>
+      <c r="C61" s="109"/>
+      <c r="D61" s="109"/>
+      <c r="E61" s="109"/>
+      <c r="F61" s="109"/>
+      <c r="G61" s="109"/>
+      <c r="H61" s="109"/>
+    </row>
+    <row r="62" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="109"/>
+      <c r="B62" s="109"/>
+      <c r="C62" s="109"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="109"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="109"/>
+      <c r="H62" s="109"/>
+    </row>
+    <row r="63" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="109"/>
+      <c r="B63" s="109"/>
+      <c r="C63" s="109"/>
+      <c r="D63" s="109"/>
+      <c r="E63" s="109"/>
+      <c r="F63" s="109"/>
+      <c r="G63" s="109"/>
+      <c r="H63" s="109"/>
+    </row>
+    <row r="64" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="109"/>
+      <c r="B64" s="109"/>
+      <c r="C64" s="109"/>
+      <c r="D64" s="109"/>
+      <c r="E64" s="109"/>
+      <c r="F64" s="109"/>
+      <c r="G64" s="109"/>
+      <c r="H64" s="109"/>
+    </row>
+    <row r="65" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="109"/>
+      <c r="B65" s="109"/>
+      <c r="C65" s="109"/>
+      <c r="D65" s="109"/>
+      <c r="E65" s="109"/>
+      <c r="F65" s="109"/>
+      <c r="G65" s="109"/>
+      <c r="H65" s="109"/>
+    </row>
+    <row r="66" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="109"/>
+      <c r="B66" s="109"/>
+      <c r="C66" s="109"/>
+      <c r="D66" s="109"/>
+      <c r="E66" s="109"/>
+      <c r="F66" s="109"/>
+      <c r="G66" s="109"/>
+      <c r="H66" s="109"/>
+    </row>
+    <row r="67" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="109"/>
+      <c r="B67" s="109"/>
+      <c r="C67" s="109"/>
+      <c r="D67" s="109"/>
+      <c r="E67" s="109"/>
+      <c r="F67" s="109"/>
+      <c r="G67" s="109"/>
+      <c r="H67" s="109"/>
+    </row>
+    <row r="68" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="109"/>
+      <c r="B68" s="109"/>
+      <c r="C68" s="109"/>
+      <c r="D68" s="109"/>
+      <c r="E68" s="109"/>
+      <c r="F68" s="109"/>
+      <c r="G68" s="109"/>
+      <c r="H68" s="109"/>
+    </row>
+    <row r="69" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="109"/>
+      <c r="B69" s="109"/>
+      <c r="C69" s="109"/>
+      <c r="D69" s="109"/>
+      <c r="E69" s="109"/>
+      <c r="F69" s="109"/>
+      <c r="G69" s="109"/>
+      <c r="H69" s="109"/>
+    </row>
+    <row r="70" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="109"/>
+      <c r="B70" s="109"/>
+      <c r="C70" s="109"/>
+      <c r="D70" s="109"/>
+      <c r="E70" s="109"/>
+      <c r="F70" s="109"/>
+      <c r="G70" s="109"/>
+      <c r="H70" s="109"/>
+    </row>
+    <row r="71" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="109"/>
+      <c r="B71" s="109"/>
+      <c r="C71" s="109"/>
+      <c r="D71" s="109"/>
+      <c r="E71" s="109"/>
+      <c r="F71" s="109"/>
+      <c r="G71" s="109"/>
+      <c r="H71" s="109"/>
+    </row>
+    <row r="72" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="109"/>
+      <c r="B72" s="109"/>
+      <c r="C72" s="109"/>
+      <c r="D72" s="109"/>
+      <c r="E72" s="109"/>
+      <c r="F72" s="109"/>
+      <c r="G72" s="109"/>
+      <c r="H72" s="109"/>
+    </row>
+    <row r="73" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="109"/>
+      <c r="B73" s="109"/>
+      <c r="C73" s="109"/>
+      <c r="D73" s="109"/>
+      <c r="E73" s="109"/>
+      <c r="F73" s="109"/>
+      <c r="G73" s="109"/>
+      <c r="H73" s="109"/>
+    </row>
+    <row r="74" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="109"/>
+      <c r="B74" s="109"/>
+      <c r="C74" s="109"/>
+      <c r="D74" s="109"/>
+      <c r="E74" s="109"/>
+      <c r="F74" s="109"/>
+      <c r="G74" s="109"/>
+      <c r="H74" s="109"/>
+    </row>
+    <row r="75" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="109"/>
+      <c r="B75" s="109"/>
+      <c r="C75" s="109"/>
+      <c r="D75" s="109"/>
+      <c r="E75" s="109"/>
+      <c r="F75" s="109"/>
+      <c r="G75" s="109"/>
+      <c r="H75" s="109"/>
+    </row>
+    <row r="76" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="109"/>
+      <c r="B76" s="109"/>
+      <c r="C76" s="109"/>
+      <c r="D76" s="109"/>
+      <c r="E76" s="109"/>
+      <c r="F76" s="109"/>
+      <c r="G76" s="109"/>
+      <c r="H76" s="109"/>
+    </row>
+    <row r="77" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="109"/>
+      <c r="B77" s="109"/>
+      <c r="C77" s="109"/>
+      <c r="D77" s="109"/>
+      <c r="E77" s="109"/>
+      <c r="F77" s="109"/>
+      <c r="G77" s="109"/>
+      <c r="H77" s="109"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="58">
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="F34:H34"/>
@@ -2767,18 +2741,49 @@
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="B44:E44"/>
-    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="C38:H38"/>
-    <mergeCell ref="B48:G49"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:F49"/>
     <mergeCell ref="A51:H51"/>
-    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A77:H77"/>
   </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="46" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>